--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484293_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484293_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.7651</v>
+        <v>8.008599999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>8.9717</v>
+        <v>9.0322</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2065</v>
+        <v>-1.0236</v>
       </c>
       <c r="G2" t="n">
         <v>3.7139</v>
@@ -610,13 +610,13 @@
         <v>2.1488</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3135</v>
+        <v>-0.4431</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3548</v>
+        <v>-0.2943</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6682</v>
+        <v>-0.1488</v>
       </c>
       <c r="V2" t="n">
         <v>4.5424</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.943</v>
+        <v>2.7602</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0672</v>
+        <v>2.9661</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1242</v>
+        <v>-0.2059</v>
       </c>
       <c r="G3" t="n">
         <v>0.4452</v>
@@ -688,13 +688,13 @@
         <v>0.9767</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0253</v>
+        <v>-0.1576</v>
       </c>
       <c r="T3" t="n">
-        <v>0.432</v>
+        <v>0.3309</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4068</v>
+        <v>-0.4885</v>
       </c>
       <c r="V3" t="n">
         <v>1.4959</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3542</v>
+        <v>1.1774</v>
       </c>
       <c r="E4" t="n">
-        <v>2.5703</v>
+        <v>2.5298</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.2162</v>
+        <v>-1.3523</v>
       </c>
       <c r="G4" t="n">
         <v>1.7854</v>
@@ -766,13 +766,13 @@
         <v>0.9767</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.09909999999999999</v>
+        <v>-0.2759</v>
       </c>
       <c r="T4" t="n">
-        <v>0.311</v>
+        <v>0.2704</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4101</v>
+        <v>-0.5463</v>
       </c>
       <c r="V4" t="n">
         <v>-0.3321</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. VIDAL RAMOS</t>
+          <t>R. BORGES PINO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1227</v>
+        <v>0.9559</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1413</v>
+        <v>1.8097</v>
       </c>
       <c r="F5" t="n">
-        <v>1.264</v>
+        <v>-0.8538</v>
       </c>
       <c r="G5" t="n">
-        <v>2.2392</v>
+        <v>0.5219</v>
       </c>
       <c r="H5" t="n">
-        <v>1.7276</v>
+        <v>0.8463000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5116000000000001</v>
+        <v>-0.3243</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9248</v>
+        <v>2.3744</v>
       </c>
       <c r="K5" t="n">
-        <v>1.682</v>
+        <v>2.2934</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2428</v>
+        <v>0.0809</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3144</v>
+        <v>-1.8524</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0456</v>
+        <v>-1.4472</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2688</v>
+        <v>-0.4052</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.1721</v>
+        <v>1.3674</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7581</v>
+        <v>1.3674</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0555</v>
+        <v>-0.9334</v>
       </c>
       <c r="T5" t="n">
-        <v>0.864</v>
+        <v>-0.5646</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.8085</v>
+        <v>-0.3688</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. BORGES PINO</t>
+          <t>F. VIDAL RAMOS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6914</v>
+        <v>0.7727000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7086</v>
+        <v>-0.5458</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.0172</v>
+        <v>1.3185</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5219</v>
+        <v>2.2392</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8463000000000001</v>
+        <v>1.7276</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3243</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>2.3744</v>
+        <v>1.9248</v>
       </c>
       <c r="K6" t="n">
-        <v>2.2934</v>
+        <v>1.682</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0809</v>
+        <v>0.2428</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.8524</v>
+        <v>0.3144</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.4472</v>
+        <v>0.0456</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4052</v>
+        <v>0.2688</v>
       </c>
       <c r="P6" t="n">
-        <v>1.3674</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.9301</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3674</v>
+        <v>1.7581</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.1979</v>
+        <v>-0.2945</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6657</v>
+        <v>0.4596</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5322</v>
+        <v>-0.754</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8843</v>
+        <v>-1.1659</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7413999999999999</v>
+        <v>0.2963</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.6257</v>
+        <v>-1.4622</v>
       </c>
       <c r="G7" t="n">
         <v>2.2984</v>
@@ -1000,13 +1000,13 @@
         <v>1.9534</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6395</v>
+        <v>-0.9211</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4404</v>
+        <v>-0.0047</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.0798</v>
+        <v>-0.9164</v>
       </c>
       <c r="V7" t="n">
         <v>0.3869</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.7726</v>
+        <v>-1.2259</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7943</v>
+        <v>-0.3293</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9782999999999999</v>
+        <v>-0.8966</v>
       </c>
       <c r="G8" t="n">
         <v>-0.8270999999999999</v>
@@ -1078,13 +1078,13 @@
         <v>0.1953</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5316</v>
+        <v>0.0151</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1816</v>
+        <v>0.2834</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.35</v>
+        <v>-0.2683</v>
       </c>
       <c r="V8" t="n">
         <v>-0.6093</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L. PERALTA VISTUE</t>
+          <t>P. CABAÑERO PUERTAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1613</v>
+        <v>-2.1998</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3476</v>
+        <v>-1.1757</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.8137</v>
+        <v>-1.0242</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1572</v>
+        <v>1.5244</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.0762</v>
+        <v>1.4843</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0809</v>
+        <v>0.0401</v>
       </c>
       <c r="J9" t="n">
-        <v>0.076</v>
+        <v>3.7266</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0217</v>
+        <v>3.011</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0543</v>
+        <v>0.7156</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.2332</v>
+        <v>-2.2022</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.098</v>
+        <v>-1.5267</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1352</v>
+        <v>-0.6755</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.7814</v>
+        <v>-3.7115</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9767</v>
+        <v>-5.8603</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1953</v>
+        <v>2.1488</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0545</v>
+        <v>-0.9540999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5531</v>
+        <v>-0.2606</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4986</v>
+        <v>-0.6935</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2772</v>
+        <v>0.9414</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X9" t="n">
         <v>-0.2772</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. CASTELLO LOGROÑO</t>
+          <t>L. PERALTA VISTUE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8664</v>
+        <v>-2.2818</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6499</v>
+        <v>-0.5499000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.2164</v>
+        <v>-1.732</v>
       </c>
       <c r="G10" t="n">
-        <v>1.2405</v>
+        <v>-1.1572</v>
       </c>
       <c r="H10" t="n">
-        <v>1.2543</v>
+        <v>-1.0762</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0138</v>
+        <v>-0.0809</v>
       </c>
       <c r="J10" t="n">
-        <v>2.7488</v>
+        <v>0.076</v>
       </c>
       <c r="K10" t="n">
-        <v>2.0875</v>
+        <v>0.0217</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6613</v>
+        <v>0.0543</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.5083</v>
+        <v>-1.2332</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8332000000000001</v>
+        <v>-1.098</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6751</v>
+        <v>-0.1352</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R10" t="n">
-        <v>1.9534</v>
+        <v>0.1953</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.2827</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7262999999999999</v>
+        <v>0.3508</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5564</v>
+        <v>-0.4169</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.8242</v>
+        <v>-0.2772</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.719</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.1052</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. CABAÑERO PUERTAS</t>
+          <t>J. CASTELLO LOGROÑO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.2405</v>
+        <v>-2.5474</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.944</v>
+        <v>-0.5488</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2965</v>
+        <v>-1.9985</v>
       </c>
       <c r="G11" t="n">
-        <v>1.5244</v>
+        <v>1.2405</v>
       </c>
       <c r="H11" t="n">
-        <v>1.4843</v>
+        <v>1.2543</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0401</v>
+        <v>-0.0138</v>
       </c>
       <c r="J11" t="n">
-        <v>3.7266</v>
+        <v>2.7488</v>
       </c>
       <c r="K11" t="n">
-        <v>3.011</v>
+        <v>2.0875</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7156</v>
+        <v>0.6613</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.2022</v>
+        <v>-1.5083</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.5267</v>
+        <v>-0.8332000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6755</v>
+        <v>-0.6751</v>
       </c>
       <c r="P11" t="n">
-        <v>-3.7115</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-5.8603</v>
+        <v>-1.9534</v>
       </c>
       <c r="R11" t="n">
-        <v>2.1488</v>
+        <v>1.9534</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.9948</v>
+        <v>-0.9637</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0289</v>
+        <v>-0.6252</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.9659</v>
+        <v>-0.3385</v>
       </c>
       <c r="V11" t="n">
-        <v>0.9414</v>
+        <v>-2.8242</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2186</v>
+        <v>-0.719</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.2772</v>
+        <v>-2.1052</v>
       </c>
     </row>
     <row r="12">
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.951299999999999</v>
+        <v>4.254</v>
       </c>
       <c r="E12" t="n">
-        <v>13.1821</v>
+        <v>13.4846</v>
       </c>
       <c r="F12" t="n">
-        <v>-9.230699999999999</v>
+        <v>-9.230599999999999</v>
       </c>
       <c r="G12" t="n">
         <v>11.7846</v>
       </c>
       <c r="H12" t="n">
-        <v>4.3697</v>
+        <v>4.369699999999999</v>
       </c>
       <c r="I12" t="n">
         <v>7.4152</v>
@@ -1381,7 +1381,7 @@
         <v>-0.6819999999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>-5.8604</v>
+        <v>-5.860399999999999</v>
       </c>
       <c r="Q12" t="n">
         <v>-19.5342</v>
@@ -1390,22 +1390,22 @@
         <v>13.6739</v>
       </c>
       <c r="S12" t="n">
-        <v>-5.296799999999999</v>
+        <v>-4.9944</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3567999999999998</v>
+        <v>-0.05430000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-4.9401</v>
+        <v>-4.94</v>
       </c>
       <c r="V12" t="n">
-        <v>3.3238</v>
+        <v>3.323800000000001</v>
       </c>
       <c r="W12" t="n">
         <v>9.5297</v>
       </c>
       <c r="X12" t="n">
-        <v>-6.205699999999999</v>
+        <v>-6.2057</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.551</v>
+        <v>5.539</v>
       </c>
       <c r="E13" t="n">
-        <v>5.6354</v>
+        <v>6.2421</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.0844</v>
+        <v>-0.7030999999999999</v>
       </c>
       <c r="G13" t="n">
         <v>5.0169</v>
@@ -1468,13 +1468,13 @@
         <v>2.1488</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.384</v>
+        <v>0.604</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1594</v>
+        <v>0.4472</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2246</v>
+        <v>0.1567</v>
       </c>
       <c r="V13" t="n">
         <v>-0.2772</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.727</v>
+        <v>1.6882</v>
       </c>
       <c r="E14" t="n">
-        <v>2.733</v>
+        <v>2.5308</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.006</v>
+        <v>-0.8426</v>
       </c>
       <c r="G14" t="n">
         <v>-0.8011</v>
@@ -1546,13 +1546,13 @@
         <v>3.1255</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6566</v>
+        <v>0.6178</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8256</v>
+        <v>0.6234</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.169</v>
+        <v>-0.0056</v>
       </c>
       <c r="V14" t="n">
         <v>-0.2772</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. HERETER MARCHANTE</t>
+          <t>M. SUAREZ CANOSA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7847</v>
+        <v>0.97</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2632</v>
+        <v>0.6946</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4785</v>
+        <v>0.2754</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.8389</v>
+        <v>-0.3726</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.8522</v>
+        <v>0.1264</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0132</v>
+        <v>-0.499</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9987</v>
+        <v>0.451</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3108</v>
+        <v>1.0847</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6879</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.8377</v>
+        <v>-0.8237</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.163</v>
+        <v>-0.9583</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6747</v>
+        <v>0.1346</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.586</v>
+        <v>1.1721</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3674</v>
+        <v>1.1721</v>
       </c>
       <c r="S15" t="n">
-        <v>2.5418</v>
+        <v>0.1706</v>
       </c>
       <c r="T15" t="n">
-        <v>2.2727</v>
+        <v>0.2436</v>
       </c>
       <c r="U15" t="n">
-        <v>0.269</v>
+        <v>-0.07290000000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.0549</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. SUAREZ CANOSA</t>
+          <t>H. DEL RIO GASPAR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2816</v>
+        <v>-0.096</v>
       </c>
       <c r="E16" t="n">
-        <v>0.08790000000000001</v>
+        <v>0.4122</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1937</v>
+        <v>-0.5083</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.3726</v>
+        <v>-0.2831</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1264</v>
+        <v>-0.1481</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.499</v>
+        <v>-0.135</v>
       </c>
       <c r="J16" t="n">
-        <v>0.451</v>
+        <v>0.0614</v>
       </c>
       <c r="K16" t="n">
-        <v>1.0847</v>
+        <v>0.0614</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6336000000000001</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8237</v>
+        <v>-0.3445</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9583</v>
+        <v>-0.2095</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1346</v>
+        <v>-0.135</v>
       </c>
       <c r="P16" t="n">
-        <v>1.1721</v>
+        <v>0.1953</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1721</v>
+        <v>0.1953</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5178</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3631</v>
+        <v>0.3508</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1546</v>
+        <v>-0.3591</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>F. VILAR FERNANDEZ</t>
+          <t>S. IBORRA BARRERA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1573</v>
+        <v>-0.2236</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6052</v>
+        <v>-1.9328</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4479</v>
+        <v>1.7092</v>
       </c>
       <c r="G17" t="n">
-        <v>-4.8481</v>
+        <v>-0.8083</v>
       </c>
       <c r="H17" t="n">
-        <v>-3.5125</v>
+        <v>1.3085</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.3356</v>
+        <v>-2.1169</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.7724</v>
+        <v>-0.5889</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.3815</v>
+        <v>2.067</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.3908</v>
+        <v>-2.6559</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.0757</v>
+        <v>-0.2194</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.131</v>
+        <v>-0.7585</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.9447</v>
+        <v>0.5391</v>
       </c>
       <c r="P17" t="n">
-        <v>0.586</v>
+        <v>-0.586</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R17" t="n">
-        <v>2.5395</v>
+        <v>1.3674</v>
       </c>
       <c r="S17" t="n">
-        <v>1.3179</v>
+        <v>0.6163</v>
       </c>
       <c r="T17" t="n">
-        <v>1.0072</v>
+        <v>0.0551</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3108</v>
+        <v>0.5612</v>
       </c>
       <c r="V17" t="n">
-        <v>3.1014</v>
+        <v>0.5545</v>
       </c>
       <c r="W17" t="n">
-        <v>3.3238</v>
+        <v>0.5545</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2224</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>H. DEL RIO GASPAR</t>
+          <t>F. VILAR FERNANDEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.079</v>
+        <v>-0.2822</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6145</v>
+        <v>0.3019</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5355</v>
+        <v>-0.5841</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2831</v>
+        <v>-4.8481</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1481</v>
+        <v>-3.5125</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.135</v>
+        <v>-1.3356</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0614</v>
+        <v>-1.7724</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0614</v>
+        <v>-1.3815</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-0.3908</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3445</v>
+        <v>-3.0757</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2095</v>
+        <v>-2.131</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.135</v>
+        <v>-0.9447</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1953</v>
+        <v>0.586</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R18" t="n">
-        <v>0.1953</v>
+        <v>2.5395</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1668</v>
+        <v>0.8784</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5531</v>
+        <v>0.7038</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3863</v>
+        <v>0.1746</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>3.1014</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>3.3238</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.2224</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. IBORRA BARRERA</t>
+          <t>G. HERETER MARCHANTE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,40 +1891,40 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4646</v>
+        <v>-0.7204</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.3372</v>
+        <v>-0.0513</v>
       </c>
       <c r="F19" t="n">
-        <v>1.8726</v>
+        <v>-0.6691</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8083</v>
+        <v>-0.8389</v>
       </c>
       <c r="H19" t="n">
-        <v>1.3085</v>
+        <v>-0.8522</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.1169</v>
+        <v>0.0132</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5889</v>
+        <v>0.9987</v>
       </c>
       <c r="K19" t="n">
-        <v>2.067</v>
+        <v>0.3108</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.6559</v>
+        <v>0.6879</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2194</v>
+        <v>-1.8377</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7585</v>
+        <v>-1.163</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5391</v>
+        <v>-0.6747</v>
       </c>
       <c r="P19" t="n">
         <v>-0.586</v>
@@ -1936,22 +1936,22 @@
         <v>1.3674</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3752</v>
+        <v>1.0366</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3494</v>
+        <v>0.9582000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7246</v>
+        <v>0.0784</v>
       </c>
       <c r="V19" t="n">
-        <v>0.5545</v>
+        <v>-0.3321</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5545</v>
+        <v>-0.0549</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7459</v>
+        <v>-1.5354</v>
       </c>
       <c r="E20" t="n">
-        <v>1.0994</v>
+        <v>0.3916</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.8452</v>
+        <v>-1.927</v>
       </c>
       <c r="G20" t="n">
         <v>-1.4794</v>
@@ -2014,13 +2014,13 @@
         <v>2.5395</v>
       </c>
       <c r="S20" t="n">
-        <v>1.6982</v>
+        <v>0.9087</v>
       </c>
       <c r="T20" t="n">
-        <v>1.2493</v>
+        <v>0.5415</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4489</v>
+        <v>0.3672</v>
       </c>
       <c r="V20" t="n">
         <v>-1.5507</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.8321</v>
+        <v>-2.1239</v>
       </c>
       <c r="E21" t="n">
-        <v>3.2275</v>
+        <v>3.1264</v>
       </c>
       <c r="F21" t="n">
-        <v>-5.0597</v>
+        <v>-5.2503</v>
       </c>
       <c r="G21" t="n">
         <v>-1.3465</v>
@@ -2092,13 +2092,13 @@
         <v>1.7581</v>
       </c>
       <c r="S21" t="n">
-        <v>0.8028999999999999</v>
+        <v>0.5111</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5614</v>
+        <v>0.4603</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2415</v>
+        <v>0.0508</v>
       </c>
       <c r="V21" t="n">
         <v>-3.0466</v>
@@ -2125,10 +2125,10 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.1614</v>
+        <v>-3.1503</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.9957</v>
+        <v>-1.9845</v>
       </c>
       <c r="F22" t="n">
         <v>-1.1657</v>
@@ -2170,10 +2170,10 @@
         <v>2.3441</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.084</v>
+        <v>-0.0728</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8473000000000001</v>
+        <v>0.1638</v>
       </c>
       <c r="U22" t="n">
         <v>-0.2367</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.3279</v>
+        <v>-4.0167</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.7025</v>
+        <v>-0.5003</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.6254</v>
+        <v>-3.5164</v>
       </c>
       <c r="G23" t="n">
         <v>-2.8325</v>
@@ -2248,13 +2248,13 @@
         <v>0.9767</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2767</v>
+        <v>0.0344</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1899</v>
+        <v>0.3921</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4667</v>
+        <v>-0.3577</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2186</v>
@@ -2284,7 +2284,7 @@
         <v>-3.9513</v>
       </c>
       <c r="E24" t="n">
-        <v>9.230699999999999</v>
+        <v>9.230700000000001</v>
       </c>
       <c r="F24" t="n">
         <v>-13.182</v>
@@ -2293,10 +2293,10 @@
         <v>-11.7845</v>
       </c>
       <c r="H24" t="n">
-        <v>-4.369499999999999</v>
+        <v>-4.3695</v>
       </c>
       <c r="I24" t="n">
-        <v>-7.4153</v>
+        <v>-7.415299999999999</v>
       </c>
       <c r="J24" t="n">
         <v>11.7589</v>
@@ -2329,7 +2329,7 @@
         <v>5.296899999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>4.94</v>
+        <v>4.9398</v>
       </c>
       <c r="U24" t="n">
         <v>0.3569</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484293_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484293_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,11 +632,16 @@
       <c r="X2" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484293_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. FLOREN LARIO</t>
+          <t>P. CABAÑERO PUERTAS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +653,78 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7602</v>
+        <v>3.9699</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9661</v>
+        <v>3.9699</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2059</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4452</v>
+        <v>3.9699</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2287</v>
+        <v>2.1489</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6739000000000001</v>
+        <v>1.821</v>
       </c>
       <c r="J3" t="n">
-        <v>1.1393</v>
+        <v>3.9699</v>
       </c>
       <c r="K3" t="n">
-        <v>0.33</v>
+        <v>2.1489</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8093</v>
+        <v>1.821</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.6941000000000001</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5587</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1354</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1576</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3309</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4885</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484293_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. RAMOS SAINZ</t>
+          <t>D. FLOREN LARIO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +736,78 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1774</v>
+        <v>2.7602</v>
       </c>
       <c r="E4" t="n">
-        <v>2.5298</v>
+        <v>2.9661</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.3523</v>
+        <v>-0.2059</v>
       </c>
       <c r="G4" t="n">
-        <v>1.7854</v>
+        <v>0.4452</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.4262</v>
+        <v>-0.2287</v>
       </c>
       <c r="I4" t="n">
-        <v>2.2116</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>1.7402</v>
+        <v>1.1393</v>
       </c>
       <c r="K4" t="n">
-        <v>0.472</v>
+        <v>0.33</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2683</v>
+        <v>0.8093</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0452</v>
+        <v>-0.6941000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8982</v>
+        <v>-0.5587</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9433</v>
+        <v>-0.1354</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>0.9767</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0.9767</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2759</v>
+        <v>-0.1576</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2704</v>
+        <v>0.3309</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5463</v>
+        <v>-0.4885</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3321</v>
+        <v>1.4959</v>
       </c>
       <c r="W4" t="n">
         <v>1.4959</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.8279</v>
+        <v>0</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484293_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. BORGES PINO</t>
+          <t>P. RAMOS SAINZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +819,78 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9559</v>
+        <v>1.1774</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8097</v>
+        <v>2.5298</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.8538</v>
+        <v>-1.3523</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5219</v>
+        <v>1.7854</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8463000000000001</v>
+        <v>-0.4262</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3243</v>
+        <v>2.2116</v>
       </c>
       <c r="J5" t="n">
-        <v>2.3744</v>
+        <v>1.7402</v>
       </c>
       <c r="K5" t="n">
-        <v>2.2934</v>
+        <v>0.472</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0809</v>
+        <v>1.2683</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.8524</v>
+        <v>0.0452</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.4472</v>
+        <v>-0.8982</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4052</v>
+        <v>0.9433</v>
       </c>
       <c r="P5" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3674</v>
+        <v>0.9767</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9334</v>
+        <v>-0.2759</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5646</v>
+        <v>0.2704</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3688</v>
+        <v>-0.5463</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.3321</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.4959</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.8279</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484293_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F. VIDAL RAMOS</t>
+          <t>R. BORGES PINO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +902,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7727000000000001</v>
+        <v>0.9559</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5458</v>
+        <v>1.8097</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3185</v>
+        <v>-0.8538</v>
       </c>
       <c r="G6" t="n">
-        <v>2.2392</v>
+        <v>0.5219</v>
       </c>
       <c r="H6" t="n">
-        <v>1.7276</v>
+        <v>0.8463000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5116000000000001</v>
+        <v>-0.3243</v>
       </c>
       <c r="J6" t="n">
-        <v>1.9248</v>
+        <v>2.3744</v>
       </c>
       <c r="K6" t="n">
-        <v>1.682</v>
+        <v>2.2934</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2428</v>
+        <v>0.0809</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3144</v>
+        <v>-1.8524</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0456</v>
+        <v>-1.4472</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2688</v>
+        <v>-0.4052</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.1721</v>
+        <v>1.3674</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7581</v>
+        <v>1.3674</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2945</v>
+        <v>-0.9334</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4596</v>
+        <v>-0.5646</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.754</v>
+        <v>-0.3688</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -938,12 +963,17 @@
       </c>
       <c r="X6" t="n">
         <v>0</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484293_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. CASADO FAJO</t>
+          <t>F. VIDAL RAMOS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +985,78 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1659</v>
+        <v>0.7727000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2963</v>
+        <v>-0.5458</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.4622</v>
+        <v>1.3185</v>
       </c>
       <c r="G7" t="n">
-        <v>2.2984</v>
+        <v>2.2392</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2346</v>
+        <v>1.7276</v>
       </c>
       <c r="I7" t="n">
-        <v>2.0638</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>3.9659</v>
+        <v>1.9248</v>
       </c>
       <c r="K7" t="n">
-        <v>2.1706</v>
+        <v>1.682</v>
       </c>
       <c r="L7" t="n">
-        <v>1.7953</v>
+        <v>0.2428</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.6676</v>
+        <v>0.3144</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.936</v>
+        <v>0.0456</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2685</v>
+        <v>0.2688</v>
       </c>
       <c r="P7" t="n">
+        <v>-1.1721</v>
+      </c>
+      <c r="Q7" t="n">
         <v>-2.9301</v>
       </c>
-      <c r="Q7" t="n">
-        <v>-4.8836</v>
-      </c>
       <c r="R7" t="n">
-        <v>1.9534</v>
+        <v>1.7581</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9211</v>
+        <v>-0.2945</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0047</v>
+        <v>0.4596</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9164</v>
+        <v>-0.754</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3869</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.8317</v>
+        <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484293_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. ANCISO SANTANDER</t>
+          <t>J. CASTELLO LOGROÑO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2259</v>
+        <v>0.307</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3293</v>
+        <v>0.307</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8966</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8270999999999999</v>
+        <v>0.307</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6922</v>
+        <v>0.307</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1348</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6127</v>
+        <v>0.307</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0614</v>
+        <v>0.307</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6741</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2144</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7536</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5393</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0151</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2834</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2683</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484293_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. CABAÑERO PUERTAS</t>
+          <t>M. CASADO FAJO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1998</v>
+        <v>-1.1659</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1757</v>
+        <v>0.2963</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0242</v>
+        <v>-1.4622</v>
       </c>
       <c r="G9" t="n">
-        <v>1.5244</v>
+        <v>2.2984</v>
       </c>
       <c r="H9" t="n">
-        <v>1.4843</v>
+        <v>0.2346</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0401</v>
+        <v>2.0638</v>
       </c>
       <c r="J9" t="n">
-        <v>3.7266</v>
+        <v>3.9659</v>
       </c>
       <c r="K9" t="n">
-        <v>3.011</v>
+        <v>2.1706</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7156</v>
+        <v>1.7953</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.2022</v>
+        <v>-1.6676</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.5267</v>
+        <v>-1.936</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6755</v>
+        <v>0.2685</v>
       </c>
       <c r="P9" t="n">
-        <v>-3.7115</v>
+        <v>-2.9301</v>
       </c>
       <c r="Q9" t="n">
-        <v>-5.8603</v>
+        <v>-4.8836</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1488</v>
+        <v>1.9534</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9540999999999999</v>
+        <v>-0.9211</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2606</v>
+        <v>-0.0047</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6935</v>
+        <v>-0.9164</v>
       </c>
       <c r="V9" t="n">
-        <v>0.9414</v>
+        <v>0.3869</v>
       </c>
       <c r="W9" t="n">
         <v>1.2186</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2772</v>
+        <v>-0.8317</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484293_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L. PERALTA VISTUE</t>
+          <t>S. ANCISO SANTANDER</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.2818</v>
+        <v>-1.2259</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5499000000000001</v>
+        <v>-0.3293</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.732</v>
+        <v>-0.8966</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.1572</v>
+        <v>-0.8270999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.0762</v>
+        <v>-0.6922</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0809</v>
+        <v>-0.1348</v>
       </c>
       <c r="J10" t="n">
-        <v>0.076</v>
+        <v>-0.6127</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0217</v>
+        <v>0.0614</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0543</v>
+        <v>-0.6741</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.2332</v>
+        <v>-0.2144</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.098</v>
+        <v>-0.7536</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1352</v>
+        <v>0.5393</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.7814</v>
+        <v>0.1953</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0.1953</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.06610000000000001</v>
+        <v>0.0151</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3508</v>
+        <v>0.2834</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4169</v>
+        <v>-0.2683</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2772</v>
+        <v>-0.6093</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2772</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484293_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. CASTELLO LOGROÑO</t>
+          <t>L. PERALTA VISTUE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.5474</v>
+        <v>-2.2818</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.5488</v>
+        <v>-0.5499000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.9985</v>
+        <v>-1.732</v>
       </c>
       <c r="G11" t="n">
-        <v>1.2405</v>
+        <v>-1.1572</v>
       </c>
       <c r="H11" t="n">
-        <v>1.2543</v>
+        <v>-1.0762</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.0138</v>
+        <v>-0.0809</v>
       </c>
       <c r="J11" t="n">
-        <v>2.7488</v>
+        <v>0.076</v>
       </c>
       <c r="K11" t="n">
-        <v>2.0875</v>
+        <v>0.0217</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6613</v>
+        <v>0.0543</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.5083</v>
+        <v>-1.2332</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.8332000000000001</v>
+        <v>-1.098</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6751</v>
+        <v>-0.1352</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R11" t="n">
-        <v>1.9534</v>
+        <v>0.1953</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9637</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6252</v>
+        <v>0.3508</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3385</v>
+        <v>-0.4169</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.8242</v>
+        <v>-0.2772</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.719</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.1052</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484293_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>J. CASTELLO LOGRONO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,292 +1400,303 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.254</v>
+        <v>-2.8544</v>
       </c>
       <c r="E12" t="n">
-        <v>13.4846</v>
+        <v>-0.8558</v>
       </c>
       <c r="F12" t="n">
-        <v>-9.230599999999999</v>
+        <v>-1.9985</v>
       </c>
       <c r="G12" t="n">
-        <v>11.7846</v>
+        <v>0.9335</v>
       </c>
       <c r="H12" t="n">
-        <v>4.369699999999999</v>
+        <v>0.9473</v>
       </c>
       <c r="I12" t="n">
-        <v>7.4152</v>
+        <v>-0.0138</v>
       </c>
       <c r="J12" t="n">
-        <v>23.5435</v>
+        <v>2.4418</v>
       </c>
       <c r="K12" t="n">
-        <v>15.4463</v>
+        <v>1.7805</v>
       </c>
       <c r="L12" t="n">
-        <v>8.097199999999999</v>
+        <v>0.6613</v>
       </c>
       <c r="M12" t="n">
-        <v>-11.7589</v>
+        <v>-1.5083</v>
       </c>
       <c r="N12" t="n">
-        <v>-11.0768</v>
+        <v>-0.8332000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.6819999999999999</v>
+        <v>-0.6751</v>
       </c>
       <c r="P12" t="n">
-        <v>-5.860399999999999</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-19.5342</v>
+        <v>-1.9534</v>
       </c>
       <c r="R12" t="n">
-        <v>13.6739</v>
+        <v>1.9534</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.9944</v>
+        <v>-0.9637</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.05430000000000001</v>
+        <v>-0.6252</v>
       </c>
       <c r="U12" t="n">
-        <v>-4.94</v>
+        <v>-0.3385</v>
       </c>
       <c r="V12" t="n">
-        <v>3.323800000000001</v>
+        <v>-2.8242</v>
       </c>
       <c r="W12" t="n">
-        <v>9.5297</v>
+        <v>-0.719</v>
       </c>
       <c r="X12" t="n">
-        <v>-6.2057</v>
+        <v>-2.1052</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484293_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P. CARRIÓN SORIANO</t>
+          <t>P. CABANERO PUERTAS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>FRIVALCA LA MUELA</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.539</v>
+        <v>-6.1697</v>
       </c>
       <c r="E13" t="n">
-        <v>6.2421</v>
+        <v>-5.1455</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7030999999999999</v>
+        <v>-1.0242</v>
       </c>
       <c r="G13" t="n">
-        <v>5.0169</v>
+        <v>-2.4455</v>
       </c>
       <c r="H13" t="n">
-        <v>2.2789</v>
+        <v>-0.6646</v>
       </c>
       <c r="I13" t="n">
-        <v>2.738</v>
+        <v>-1.7809</v>
       </c>
       <c r="J13" t="n">
-        <v>7.7483</v>
+        <v>-0.2433</v>
       </c>
       <c r="K13" t="n">
-        <v>3.9307</v>
+        <v>0.8621</v>
       </c>
       <c r="L13" t="n">
-        <v>3.8176</v>
+        <v>-1.1054</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.7314</v>
+        <v>-2.2022</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.6518</v>
+        <v>-1.5267</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.0795</v>
+        <v>-0.6755</v>
       </c>
       <c r="P13" t="n">
-        <v>0.1953</v>
+        <v>-3.7115</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.9534</v>
+        <v>-5.8603</v>
       </c>
       <c r="R13" t="n">
         <v>2.1488</v>
       </c>
       <c r="S13" t="n">
-        <v>0.604</v>
+        <v>-0.9540999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4472</v>
+        <v>-0.2606</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1567</v>
+        <v>-0.6935</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.2772</v>
+        <v>0.9414</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X13" t="n">
         <v>-0.2772</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484293_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. JAIME BATLLE</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>FRIVALCA LA MUELA</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.6882</v>
+        <v>4.254000000000002</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5308</v>
+        <v>13.4847</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.8426</v>
+        <v>-9.230600000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.8011</v>
+        <v>11.7846</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.6252</v>
+        <v>4.3697</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8241000000000001</v>
+        <v>7.4152</v>
       </c>
       <c r="J14" t="n">
-        <v>2.8841</v>
+        <v>23.5435</v>
       </c>
       <c r="K14" t="n">
-        <v>0.5756</v>
+        <v>15.4463</v>
       </c>
       <c r="L14" t="n">
-        <v>2.3085</v>
+        <v>8.097200000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.6852</v>
+        <v>-11.7589</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.2008</v>
+        <v>-11.0768</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.4844</v>
+        <v>-0.6819999999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1488</v>
+        <v>-5.8604</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9767</v>
+        <v>-19.5342</v>
       </c>
       <c r="R14" t="n">
-        <v>3.1255</v>
+        <v>13.6739</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6178</v>
+        <v>-4.994400000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6234</v>
+        <v>-0.05430000000000007</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0056</v>
+        <v>-4.94</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.2772</v>
+        <v>3.3238</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>9.529700000000002</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2772</v>
-      </c>
+        <v>-6.205699999999999</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. SUAREZ CANOSA</t>
+          <t>P. CARRIÓN SORIANO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.97</v>
+        <v>3.6489</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6946</v>
+        <v>3.6489</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.3726</v>
+        <v>3.6489</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1264</v>
+        <v>0.614</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.499</v>
+        <v>3.0349</v>
       </c>
       <c r="J15" t="n">
-        <v>0.451</v>
+        <v>3.6489</v>
       </c>
       <c r="K15" t="n">
-        <v>1.0847</v>
+        <v>0.614</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6336000000000001</v>
+        <v>3.0349</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.8237</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.9583</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1346</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1706</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2436</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.07290000000000001</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1640,709 +1706,1087 @@
       </c>
       <c r="X15" t="n">
         <v>0</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484293_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>H. DEL RIO GASPAR</t>
+          <t>P. CARRION SORIANO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.096</v>
+        <v>1.8901</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4122</v>
+        <v>2.5932</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5083</v>
+        <v>-0.7030999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.2831</v>
+        <v>1.368</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1481</v>
+        <v>1.6649</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.135</v>
+        <v>-0.2969</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0614</v>
+        <v>4.0994</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0614</v>
+        <v>3.3167</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>0.7827</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3445</v>
+        <v>-2.7314</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2095</v>
+        <v>-1.6518</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.135</v>
+        <v>-1.0795</v>
       </c>
       <c r="P16" t="n">
         <v>0.1953</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R16" t="n">
-        <v>0.1953</v>
+        <v>2.1488</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.008200000000000001</v>
+        <v>0.604</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3508</v>
+        <v>0.4472</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3591</v>
+        <v>0.1567</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484293_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. IBORRA BARRERA</t>
+          <t>A. JAIME BATLLE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2236</v>
+        <v>1.6882</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.9328</v>
+        <v>2.5308</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7092</v>
+        <v>-0.8426</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.8083</v>
+        <v>-0.8011</v>
       </c>
       <c r="H17" t="n">
-        <v>1.3085</v>
+        <v>-1.6252</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.1169</v>
+        <v>0.8241000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.5889</v>
+        <v>2.8841</v>
       </c>
       <c r="K17" t="n">
-        <v>2.067</v>
+        <v>0.5756</v>
       </c>
       <c r="L17" t="n">
-        <v>-2.6559</v>
+        <v>2.3085</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2194</v>
+        <v>-3.6852</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7585</v>
+        <v>-2.2008</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5391</v>
+        <v>-1.4844</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.586</v>
+        <v>2.1488</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3674</v>
+        <v>3.1255</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6163</v>
+        <v>0.6178</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0551</v>
+        <v>0.6234</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5612</v>
+        <v>-0.0056</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5545</v>
+        <v>-0.2772</v>
       </c>
       <c r="W17" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484293_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>F. VILAR FERNANDEZ</t>
+          <t>M. SUAREZ CANOSA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2822</v>
+        <v>0.97</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3019</v>
+        <v>0.6946</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5841</v>
+        <v>0.2754</v>
       </c>
       <c r="G18" t="n">
-        <v>-4.8481</v>
+        <v>-0.3726</v>
       </c>
       <c r="H18" t="n">
-        <v>-3.5125</v>
+        <v>0.1264</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.3356</v>
+        <v>-0.499</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.7724</v>
+        <v>0.451</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.3815</v>
+        <v>1.0847</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.3908</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.0757</v>
+        <v>-0.8237</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.131</v>
+        <v>-0.9583</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.9447</v>
+        <v>0.1346</v>
       </c>
       <c r="P18" t="n">
-        <v>0.586</v>
+        <v>1.1721</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.5395</v>
+        <v>1.1721</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8784</v>
+        <v>0.1706</v>
       </c>
       <c r="T18" t="n">
-        <v>0.7038</v>
+        <v>0.2436</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1746</v>
+        <v>-0.07290000000000001</v>
       </c>
       <c r="V18" t="n">
-        <v>3.1014</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>3.3238</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2224</v>
+        <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484293_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. HERETER MARCHANTE</t>
+          <t>A. ABELLO GIRVÉS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7204</v>
+        <v>0.307</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0513</v>
+        <v>0.307</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6691</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8389</v>
+        <v>0.307</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.8522</v>
+        <v>0.307</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0132</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9987</v>
+        <v>0.307</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3108</v>
+        <v>0.307</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6879</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.8377</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.163</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6747</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.586</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1.0366</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0.9582000000000001</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0784</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.0549</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484293_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. PUERTAS GARCIA</t>
+          <t>H. DEL RIO GASPAR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5354</v>
+        <v>-0.096</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3916</v>
+        <v>0.4122</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.927</v>
+        <v>-0.5083</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.4794</v>
+        <v>-0.2831</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.2364</v>
+        <v>-0.1481</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.243</v>
+        <v>-0.135</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3077</v>
+        <v>0.0614</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8199</v>
+        <v>0.0614</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5122</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.787</v>
+        <v>-0.3445</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.0563</v>
+        <v>-0.2095</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2692</v>
+        <v>-0.135</v>
       </c>
       <c r="P20" t="n">
-        <v>0.586</v>
+        <v>0.1953</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.5395</v>
+        <v>0.1953</v>
       </c>
       <c r="S20" t="n">
-        <v>0.9087</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5415</v>
+        <v>0.3508</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3672</v>
+        <v>-0.3591</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.5507</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-3.0466</v>
+        <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484293_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I. ISERN CASES</t>
+          <t>S. IBORRA BARRERA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1239</v>
+        <v>-0.2236</v>
       </c>
       <c r="E21" t="n">
-        <v>3.1264</v>
+        <v>-1.9328</v>
       </c>
       <c r="F21" t="n">
-        <v>-5.2503</v>
+        <v>1.7092</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.3465</v>
+        <v>-0.8083</v>
       </c>
       <c r="H21" t="n">
-        <v>1.0125</v>
+        <v>1.3085</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.3591</v>
+        <v>-2.1169</v>
       </c>
       <c r="J21" t="n">
-        <v>1.7796</v>
+        <v>-0.5889</v>
       </c>
       <c r="K21" t="n">
-        <v>2.5198</v>
+        <v>2.067</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.7402</v>
+        <v>-2.6559</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.1261</v>
+        <v>-0.2194</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.5073</v>
+        <v>-0.7585</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.6188</v>
+        <v>0.5391</v>
       </c>
       <c r="P21" t="n">
-        <v>1.7581</v>
+        <v>-0.586</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R21" t="n">
-        <v>1.7581</v>
+        <v>1.3674</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5111</v>
+        <v>0.6163</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4603</v>
+        <v>0.0551</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0508</v>
+        <v>0.5612</v>
       </c>
       <c r="V21" t="n">
-        <v>-3.0466</v>
+        <v>0.5545</v>
       </c>
       <c r="W21" t="n">
-        <v>0.8865</v>
+        <v>0.5545</v>
       </c>
       <c r="X21" t="n">
-        <v>-3.9331</v>
+        <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484293_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. GALVE NAVARRO</t>
+          <t>F. VILAR FERNANDEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.1503</v>
+        <v>-0.2822</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.9845</v>
+        <v>0.3019</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1657</v>
+        <v>-0.5841</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.1909</v>
+        <v>-4.8481</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.9258</v>
+        <v>-3.5125</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.2651</v>
+        <v>-1.3356</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.1949</v>
+        <v>-1.7724</v>
       </c>
       <c r="K22" t="n">
-        <v>1.1256</v>
+        <v>-1.3815</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.3206</v>
+        <v>-0.3908</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.996</v>
+        <v>-3.0757</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.0514</v>
+        <v>-2.131</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.9445</v>
+        <v>-0.9447</v>
       </c>
       <c r="P22" t="n">
-        <v>0.3907</v>
+        <v>0.586</v>
       </c>
       <c r="Q22" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R22" t="n">
-        <v>2.3441</v>
+        <v>2.5395</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0728</v>
+        <v>0.8784</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1638</v>
+        <v>0.7038</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2367</v>
+        <v>0.1746</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.2772</v>
+        <v>3.1014</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>3.3238</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2772</v>
+        <v>-0.2224</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484293_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. ABELLO GIRVÉS</t>
+          <t>G. HERETER MARCHANTE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.0167</v>
+        <v>-0.7204</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.5003</v>
+        <v>-0.0513</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.5164</v>
+        <v>-0.6691</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.8325</v>
+        <v>-0.8389</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.7956</v>
+        <v>-0.8522</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.0369</v>
+        <v>0.0132</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0843</v>
+        <v>0.9987</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.0371</v>
+        <v>0.3108</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1214</v>
+        <v>0.6879</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.9168</v>
+        <v>-1.8377</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.7585</v>
+        <v>-1.163</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.1583</v>
+        <v>-0.6747</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>-0.586</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9767</v>
+        <v>1.3674</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0344</v>
+        <v>1.0366</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3921</v>
+        <v>0.9582000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3577</v>
+        <v>0.0784</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.2186</v>
+        <v>-0.3321</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>-0.0549</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2186</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484293_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>A. PUERTAS GARCIA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.9513</v>
+        <v>-1.5354</v>
       </c>
       <c r="E24" t="n">
+        <v>0.3916</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-1.927</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-1.4794</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-1.2364</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-0.243</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.3077</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.8199</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-0.5122</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-1.787</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-2.0563</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.2692</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2.5395</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.9087</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.5415</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.3672</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-1.5507</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.4959</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-3.0466</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484293_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>I. ISERN CASES</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SESE A</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-2.1239</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3.1264</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-5.2503</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-1.3465</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.0125</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-2.3591</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.7796</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.5198</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-0.7402</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-3.1261</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-1.5073</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-1.6188</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.7581</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.7581</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.5111</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.4603</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.0508</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-3.0466</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0.8865</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-3.9331</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484293_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>J. GALVE NAVARRO</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SESE A</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-3.1503</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-1.9845</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-1.1657</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-3.1909</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-0.9258</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-2.2651</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-0.1949</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1.1256</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-1.3206</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-2.996</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-2.0514</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-0.9445</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R26" t="n">
+        <v>2.3441</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-0.0728</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.1638</v>
+      </c>
+      <c r="U26" t="n">
+        <v>-0.2367</v>
+      </c>
+      <c r="V26" t="n">
+        <v>-0.2772</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-0.2772</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484293_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A. ABELLO GIRVES</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SESE A</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-4.3237</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-0.8073</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-3.5164</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-3.1395</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-1.1026</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-2.0369</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-0.2227</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-0.3441</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.1214</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-2.9168</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-0.7585</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-2.1583</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.0344</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0.3921</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-0.3577</v>
+      </c>
+      <c r="V27" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>play_by_play_2484293_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SESE A</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-3.951300000000001</v>
+      </c>
+      <c r="E28" t="n">
         <v>9.230700000000001</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F28" t="n">
         <v>-13.182</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G28" t="n">
         <v>-11.7845</v>
       </c>
-      <c r="H24" t="n">
-        <v>-4.3695</v>
-      </c>
-      <c r="I24" t="n">
+      <c r="H28" t="n">
+        <v>-4.369499999999999</v>
+      </c>
+      <c r="I28" t="n">
         <v>-7.415299999999999</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J28" t="n">
         <v>11.7589</v>
       </c>
-      <c r="K24" t="n">
+      <c r="K28" t="n">
         <v>11.0769</v>
       </c>
-      <c r="L24" t="n">
+      <c r="L28" t="n">
         <v>0.6820999999999997</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M28" t="n">
         <v>-23.5435</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N28" t="n">
         <v>-15.4464</v>
       </c>
-      <c r="O24" t="n">
+      <c r="O28" t="n">
         <v>-8.097</v>
       </c>
-      <c r="P24" t="n">
+      <c r="P28" t="n">
         <v>5.8603</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="Q28" t="n">
         <v>-13.6738</v>
       </c>
-      <c r="R24" t="n">
+      <c r="R28" t="n">
         <v>19.5344</v>
       </c>
-      <c r="S24" t="n">
+      <c r="S28" t="n">
         <v>5.296899999999999</v>
       </c>
-      <c r="T24" t="n">
-        <v>4.9398</v>
-      </c>
-      <c r="U24" t="n">
+      <c r="T28" t="n">
+        <v>4.939800000000001</v>
+      </c>
+      <c r="U28" t="n">
         <v>0.3569</v>
       </c>
-      <c r="V24" t="n">
-        <v>-3.3237</v>
-      </c>
-      <c r="W24" t="n">
+      <c r="V28" t="n">
+        <v>-3.323700000000001</v>
+      </c>
+      <c r="W28" t="n">
         <v>6.2058</v>
       </c>
-      <c r="X24" t="n">
+      <c r="X28" t="n">
         <v>-9.529500000000001</v>
       </c>
+      <c r="Y28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
